--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.70933</v>
+        <v>16.67623</v>
       </c>
       <c r="D2" t="n">
-        <v>16.44326</v>
+        <v>16.51948</v>
       </c>
       <c r="E2" t="n">
-        <v>16.61215</v>
+        <v>16.56977</v>
       </c>
       <c r="F2" t="n">
-        <v>42.49533</v>
+        <v>43.17258</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05044</v>
+        <v>0.05124</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81679</v>
+        <v>1.83528</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.15999</v>
+        <v>16.98938</v>
       </c>
       <c r="D3" t="n">
-        <v>16.69988</v>
+        <v>16.62746</v>
       </c>
       <c r="E3" t="n">
-        <v>16.96688</v>
+        <v>16.78772</v>
       </c>
       <c r="F3" t="n">
-        <v>43.01876</v>
+        <v>43.66304</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05084</v>
+        <v>0.05171</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79176</v>
+        <v>1.77594</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.67643</v>
+        <v>17.13123</v>
       </c>
       <c r="D4" t="n">
-        <v>16.62887</v>
+        <v>16.66492</v>
       </c>
       <c r="E4" t="n">
-        <v>16.66399</v>
+        <v>16.6827</v>
       </c>
       <c r="F4" t="n">
-        <v>42.15367</v>
+        <v>43.10754</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04882</v>
+        <v>0.05116</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81985</v>
+        <v>1.80289</v>
       </c>
     </row>
   </sheetData>
